--- a/public/templates/test_input/baocaocongtruong_daolo_10.xlsx
+++ b/public/templates/test_input/baocaocongtruong_daolo_10.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>CT Đào lò 1</t>
+          <t>Đào lò 6</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
@@ -1521,7 +1521,7 @@
       <c r="A8" s="65" t="n"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>CT Đào lò 2</t>
+          <t>Đào lò 2</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>CT Đào lò 1</t>
+          <t>Đào lò 6</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
@@ -1943,7 +1943,7 @@
       <c r="A14" s="65" t="n"/>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>CT Đào lò 2</t>
+          <t>Đào lò 2</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
@@ -2151,7 +2151,7 @@
       <c r="A17" s="65" t="n"/>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>CT Đào lò 3</t>
+          <t>Đào lò 3</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
@@ -9949,37 +9949,37 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="E8:E10"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E8:E10"/>
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="C11:C13"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D8:D10"/>
     <mergeCell ref="B11:B13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="E14:E16"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="A11:A19"/>
     <mergeCell ref="A5:A10"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="B5:B7"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A11:A19"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="M3:O3"/>
     <mergeCell ref="D11:D13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="C8:C10"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="F2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
